--- a/diseases/d209/2020-2025.xlsx
+++ b/diseases/d209/2020-2025.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">

--- a/diseases/d209/2020-2025.xlsx
+++ b/diseases/d209/2020-2025.xlsx
@@ -751,12 +751,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2023-12-09</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002911400252945365</v>
+        <v>0.0002927965786063925</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2023-12-09</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -930,125 +930,50 @@
       <c r="P3" t="n">
         <v>1</v>
       </c>
+      <c r="R3" t="n">
+        <v>0.0002927965786063925</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Hepatitis B, perinatal, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Confirmed perinatal hepatitis B series.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1150,12 +1075,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2022-11-05</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1168,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002894971273069784</v>
+        <v>0.0002927965786063925</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1187,7 +1112,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1197,7 +1122,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1210,7 +1135,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1277,7 +1202,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1312,12 +1237,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2022-12-17</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1329,125 +1254,50 @@
       <c r="P5" t="n">
         <v>1</v>
       </c>
+      <c r="R5" t="n">
+        <v>0.0002927965786063925</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Hepatitis B, perinatal, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Confirmed perinatal hepatitis B series.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1549,12 +1399,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2023-01-07</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1567,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002894971273069784</v>
+        <v>0.0002911400252945365</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1586,7 +1436,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1596,7 +1446,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1609,7 +1459,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1676,7 +1526,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1711,142 +1561,67 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0005822800505890731</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Hepatitis B, perinatal, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Confirmed perinatal hepatitis B series.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1948,12 +1723,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1966,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002879555610852622</v>
+        <v>0.0002911400252945365</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1985,7 +1760,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1995,7 +1770,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2008,7 +1783,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2075,7 +1850,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2110,12 +1885,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2127,125 +1902,50 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="n">
+        <v>0.0002911400252945365</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Hepatitis B, perinatal, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Confirmed perinatal hepatitis B series.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_US_PERINATAL_HEPATITIS_B</t>
-        </is>
-      </c>
       <c r="AT9" t="n">
         <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2347,12 +2047,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2023-12-09</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2365,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0002879555610852622</v>
+        <v>0.0002911400252945365</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2384,7 +2084,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2394,7 +2094,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2407,7 +2107,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2509,12 +2209,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2023-12-09</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2621,7 +2321,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2631,7 +2331,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2644,7 +2344,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2746,12 +2446,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2764,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002879555610852622</v>
+        <v>0.0002911400252945365</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2783,7 +2483,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2793,7 +2493,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2806,7 +2506,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2873,215 +2573,1973 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0002894971273069784</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>D209</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Perinatal hepatitis B</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>围产期乙型肝炎</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Hepatitis B, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0002894971273069784</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Hepatitis B, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0002879555610852622</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Hepatitis B, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0002879555610852622</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Hepatitis B, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.0002879555610852622</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D209</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis B</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>围产期乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>SRC_US_NNDSS</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Hepatitis B, perinatal, Confirmed</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>country:US:national</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>Confirmed perinatal hepatitis B series.</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="AN13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
         <is>
           <t>SER_US_PERINATAL_HEPATITIS_B</t>
         </is>
       </c>
-      <c r="AT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AW22" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr">
+      <c r="BA22" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BB22" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -3132,7 +4590,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-09</t>
+          <t>2022-04-02</t>
         </is>
       </c>
     </row>
@@ -3203,7 +4661,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -3213,7 +4671,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -3265,7 +4723,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
